--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104567_W13.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104567_W13.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6424</v>
+        <v>6.8358</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4592</v>
+        <v>6.5967</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1831</v>
+        <v>0.2391</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3204</v>
+        <v>0.3072</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.45</v>
+        <v>-0.4645</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7703</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>1.2015</v>
+        <v>1.1659</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1967</v>
+        <v>0.1681</v>
       </c>
       <c r="L2" t="n">
-        <v>1.0048</v>
+        <v>0.9977</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8812</v>
+        <v>-0.8587</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S2" t="n">
-        <v>0.405</v>
+        <v>0.626</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0212</v>
+        <v>0.2111</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3838</v>
+        <v>0.4149</v>
       </c>
       <c r="V2" t="n">
-        <v>5.4633</v>
+        <v>5.4474</v>
       </c>
       <c r="W2" t="n">
-        <v>5.4633</v>
+        <v>5.4474</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.052</v>
+        <v>3.4109</v>
       </c>
       <c r="E3" t="n">
-        <v>5.455</v>
+        <v>4.0192</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.403</v>
+        <v>-0.6083</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4167</v>
+        <v>3.4098</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6335</v>
+        <v>1.6315</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7832</v>
+        <v>1.7784</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4902</v>
+        <v>4.4701</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2165</v>
+        <v>2.2063</v>
       </c>
       <c r="L3" t="n">
-        <v>2.2736</v>
+        <v>2.2638</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0735</v>
+        <v>-1.0603</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8622</v>
+        <v>0.2287</v>
       </c>
       <c r="T3" t="n">
-        <v>2.099</v>
+        <v>0.6873</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2368</v>
+        <v>-0.4586</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4017</v>
+        <v>1.2375</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5566</v>
+        <v>2.2944</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1549</v>
+        <v>-1.0569</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5506</v>
+        <v>1.5298</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4991</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0497</v>
+        <v>2.0404</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6696</v>
+        <v>1.6293</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4462</v>
+        <v>0.4234</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2233</v>
+        <v>1.2058</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1189</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4815</v>
+        <v>0.36</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6593</v>
+        <v>0.1204</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1778</v>
+        <v>0.2396</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.5748</v>
+        <v>-1.5628</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.1212</v>
+        <v>-2.1075</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0466</v>
+        <v>-0.322</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5084</v>
+        <v>1.0118</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4618</v>
+        <v>-1.3338</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2488</v>
+        <v>0.2461</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2541</v>
+        <v>0.2474</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0053</v>
+        <v>-0.0013</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7008</v>
+        <v>0.673</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2558</v>
+        <v>0.2338</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4521</v>
+        <v>-0.427</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0017</v>
+        <v>0.0135</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0758</v>
+        <v>0.7003</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0344</v>
+        <v>0.5664</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0414</v>
+        <v>0.1339</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. APIC</t>
+          <t>A. KURUCS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3784</v>
+        <v>-1.0172</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4373</v>
+        <v>-0.0738</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8157</v>
+        <v>-0.9434</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2915</v>
+        <v>-1.2911</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1182</v>
+        <v>0.4538</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1733</v>
+        <v>-1.7449</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4773</v>
+        <v>0.5399</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4027</v>
+        <v>0.7272</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0746</v>
+        <v>-0.1873</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1858</v>
+        <v>-1.831</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O6" t="n">
-        <v>0.09859999999999999</v>
+        <v>-1.5576</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8084</v>
+        <v>-0.1813</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1603</v>
+        <v>0.5245</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6481</v>
+        <v>-0.7058</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.0246</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. KURUCS</t>
+          <t>D. APIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3685</v>
+        <v>-1.2486</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2751</v>
+        <v>-0.0488</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0934</v>
+        <v>-1.1998</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2796</v>
+        <v>1.2986</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4531</v>
+        <v>1.1227</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7327</v>
+        <v>0.1759</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5747</v>
+        <v>1.4707</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7375</v>
+        <v>1.3962</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1628</v>
+        <v>0.0745</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8543</v>
+        <v>-0.172</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5699</v>
+        <v>0.1014</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5426</v>
+        <v>-0.0708</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2843</v>
+        <v>-0.3115</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8269</v>
+        <v>0.2407</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.0212</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6831</v>
+        <v>-1.7985</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8059</v>
+        <v>-2.1985</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1228</v>
+        <v>0.4001</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0026</v>
+        <v>0.9913</v>
       </c>
       <c r="H8" t="n">
-        <v>0.928</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8815</v>
+        <v>0.8459</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2601</v>
+        <v>1.2336</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3786</v>
+        <v>-0.3877</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1211</v>
+        <v>0.1454</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8977000000000001</v>
+        <v>0.0117</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7652</v>
+        <v>-0.1048</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1325</v>
+        <v>0.1165</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0896</v>
+        <v>-2.7979</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0737</v>
+        <v>-0.6536</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0159</v>
+        <v>-2.1444</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2138</v>
+        <v>-1.201</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6595</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5543</v>
+        <v>-0.5432</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4839</v>
+        <v>-0.4883</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5959</v>
+        <v>-0.6</v>
       </c>
       <c r="L9" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7299</v>
+        <v>-0.7127</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1508</v>
+        <v>1.4227</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5444</v>
+        <v>0.9729</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.4498</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6094</v>
+        <v>-3.2243</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.154</v>
+        <v>-0.5818</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4554</v>
+        <v>-2.6425</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8859</v>
+        <v>-1.8805</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0115</v>
+        <v>1.0137</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.8974</v>
+        <v>-2.8942</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3889</v>
+        <v>-0.4073</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9973</v>
+        <v>0.9858</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3861</v>
+        <v>-1.3931</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4971</v>
+        <v>-1.4731</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6723</v>
+        <v>-0.3031</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5383</v>
+        <v>0.0531</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.134</v>
+        <v>-0.3562</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7044</v>
+        <v>-3.2718</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8935999999999999</v>
+        <v>1.0752</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.598</v>
+        <v>-4.347</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6978</v>
+        <v>0.667</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.3084</v>
+        <v>-3.3277</v>
       </c>
       <c r="I11" t="n">
-        <v>4.0062</v>
+        <v>3.9946</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8081</v>
+        <v>2.7573</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.7094</v>
+        <v>-2.7384</v>
       </c>
       <c r="L11" t="n">
-        <v>5.5175</v>
+        <v>5.4957</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1103</v>
+        <v>-2.0904</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4437</v>
+        <v>0.0126</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3539</v>
+        <v>0.5942</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7976</v>
+        <v>-0.5816</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7117</v>
+        <v>-3.8714</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2222</v>
+        <v>-0.6283</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.4894</v>
+        <v>-3.2431</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.2996</v>
+        <v>-2.2891</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5772</v>
+        <v>-1.5714</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-0.7178</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1356</v>
+        <v>-1.1435</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6478</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4878</v>
+        <v>-0.4917</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1639</v>
+        <v>-1.1457</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1854</v>
+        <v>0.0033</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9134</v>
+        <v>0.5152</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.728</v>
+        <v>-0.5119</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.402400000000001</v>
+        <v>-6.067499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>10.7792</v>
+        <v>10.8125</v>
       </c>
       <c r="F13" t="n">
-        <v>-17.1816</v>
+        <v>-16.88</v>
       </c>
       <c r="G13" t="n">
-        <v>1.849500000000001</v>
+        <v>1.7881</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.095799999999999</v>
+        <v>-1.1461</v>
       </c>
       <c r="I13" t="n">
-        <v>2.945299999999999</v>
+        <v>2.9341</v>
       </c>
       <c r="J13" t="n">
-        <v>11.7953</v>
+        <v>11.513</v>
       </c>
       <c r="K13" t="n">
-        <v>3.559699999999999</v>
+        <v>3.384300000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>8.2356</v>
+        <v>8.1286</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.9459</v>
+        <v>-9.725</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.6555</v>
+        <v>-4.5303</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.2904</v>
+        <v>-5.194500000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0001000000000004331</v>
+        <v>9.999999999998899e-05</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.3416</v>
+        <v>-11.3816</v>
       </c>
       <c r="R13" t="n">
-        <v>11.3416</v>
+        <v>11.3816</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4498</v>
+        <v>2.8101</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4481</v>
+        <v>3.8288</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9983</v>
+        <v>-1.0187</v>
       </c>
       <c r="V13" t="n">
-        <v>-10.7018</v>
+        <v>-10.6654</v>
       </c>
       <c r="W13" t="n">
-        <v>6.877400000000001</v>
+        <v>6.852399999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-17.5792</v>
+        <v>-17.5177</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5337</v>
+        <v>6.4948</v>
       </c>
       <c r="E14" t="n">
-        <v>7.9257</v>
+        <v>8.3506</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.392</v>
+        <v>-1.8558</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5195</v>
+        <v>3.5098</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2539</v>
+        <v>1.255</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2656</v>
+        <v>2.2548</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7557</v>
+        <v>3.7224</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4129</v>
+        <v>1.3994</v>
       </c>
       <c r="L14" t="n">
-        <v>2.3428</v>
+        <v>2.3229</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2362</v>
+        <v>-0.2125</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3053</v>
+        <v>-0.3322</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.747</v>
+        <v>-0.2744</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5583</v>
+        <v>-0.0578</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W14" t="n">
-        <v>4.917</v>
+        <v>4.9026</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1033</v>
+        <v>2.6308</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6556</v>
+        <v>1.8074</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4477</v>
+        <v>0.8235</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2634</v>
+        <v>-0.2598</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5167</v>
+        <v>-0.5115</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2532</v>
+        <v>0.2517</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1777</v>
+        <v>0.1539</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1527</v>
+        <v>-0.1659</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3304</v>
+        <v>0.3198</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4411</v>
+        <v>-0.4138</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3639</v>
+        <v>-0.3457</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9131</v>
+        <v>0.4354</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3852</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4721</v>
+        <v>-0.1286</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6629</v>
+        <v>1.9331</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6316</v>
+        <v>2.7908</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0313</v>
+        <v>-0.8577</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.9688</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1631</v>
+        <v>0.6942</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2372</v>
+        <v>0.2747</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6306</v>
+        <v>2.7283</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1806</v>
+        <v>1.3133</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4499</v>
+        <v>1.415</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7047</v>
+        <v>-1.7594</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0176</v>
+        <v>-0.6191</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6871</v>
+        <v>-1.1403</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.4025</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.5367</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7935</v>
+        <v>-0.3042</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1916</v>
+        <v>0.1599</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6018</v>
+        <v>-0.464</v>
       </c>
       <c r="V16" t="n">
-        <v>2.3461</v>
+        <v>2.1789</v>
       </c>
       <c r="W16" t="n">
-        <v>2.3461</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0746</v>
+        <v>0.625</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7007</v>
+        <v>0.8698</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.626</v>
+        <v>-0.2448</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9393</v>
+        <v>0.9267</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.1605</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2613</v>
+        <v>-0.2337</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7443</v>
+        <v>2.5983</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3263</v>
+        <v>1.1614</v>
       </c>
       <c r="L17" t="n">
-        <v>1.418</v>
+        <v>1.4369</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8051</v>
+        <v>-1.6715</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6484</v>
+        <v>-0.0009</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1567</v>
+        <v>-1.6706</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9073</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-4.5526</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1426</v>
+        <v>0.776</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0393</v>
+        <v>0.4874</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.182</v>
+        <v>0.2886</v>
       </c>
       <c r="V17" t="n">
-        <v>2.1853</v>
+        <v>2.3367</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1853</v>
+        <v>2.3367</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3979</v>
+        <v>0.5254</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9402</v>
+        <v>0.9332</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5423</v>
+        <v>-0.4078</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.6835</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1673</v>
+        <v>1.1689</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9005</v>
+        <v>0.8963</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9005</v>
+        <v>0.8963</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2236</v>
+        <v>-0.2129</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2669</v>
+        <v>0.2725</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1858,19 +1858,19 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4398</v>
+        <v>-0.3159</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.121</v>
+        <v>-0.1209</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3188</v>
+        <v>-0.195</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.107</v>
+        <v>0.2006</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0859</v>
+        <v>1.8336</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9788</v>
+        <v>-1.6331</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9508</v>
+        <v>-0.9319</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.525</v>
+        <v>-0.515</v>
       </c>
       <c r="J19" t="n">
-        <v>0.578</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.1002</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5289</v>
+        <v>-1.502</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0348</v>
+        <v>0.043</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4567</v>
+        <v>0.2228</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4915</v>
+        <v>-0.1797</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>M. HOWARD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3295</v>
+        <v>-0.598</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4978</v>
+        <v>0.8908</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8273</v>
+        <v>-1.4888</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4871</v>
+        <v>0.1515</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3969</v>
+        <v>0.5572</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0902</v>
+        <v>-0.4057</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.995</v>
+        <v>1.8403</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3952</v>
+        <v>0.9028</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5998</v>
+        <v>0.9375</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4921</v>
+        <v>-1.6888</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0017</v>
+        <v>-0.3457</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4904</v>
+        <v>-1.3432</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2268</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4525</v>
+        <v>-0.6992</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8953</v>
+        <v>-0.6229</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4428</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.8603</v>
       </c>
       <c r="W20" t="n">
-        <v>2.7317</v>
+        <v>1.9497</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7997</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. HOWARD</t>
+          <t>G. RADZEVICIUS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.266</v>
+        <v>-0.8024</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4776</v>
+        <v>0.3695</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7436</v>
+        <v>-1.172</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1624</v>
+        <v>-2.5367</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5570000000000001</v>
+        <v>-0.0522</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3946</v>
+        <v>-2.4846</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8803</v>
+        <v>-0.0599</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9685</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9594</v>
+        <v>-1.0284</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7179</v>
+        <v>-2.4769</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3639</v>
+        <v>-1.0207</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.354</v>
+        <v>-1.4562</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3888</v>
+        <v>0.5263</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0948</v>
+        <v>0.4294</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.294</v>
+        <v>0.0969</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8678</v>
+        <v>-0.1578</v>
       </c>
       <c r="W21" t="n">
-        <v>1.9604</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. RADZEVICIUS</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.43</v>
+        <v>-0.8691</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4349</v>
+        <v>0.6465</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.995</v>
+        <v>-1.5156</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5477</v>
+        <v>-1.4825</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0607</v>
+        <v>-0.3937</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.4869</v>
+        <v>-1.0888</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0357</v>
+        <v>-1.0106</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9799</v>
+        <v>-0.4072</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.0157</v>
+        <v>-0.6035</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5119</v>
+        <v>-0.4719</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0407</v>
+        <v>0.0135</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4712</v>
+        <v>-0.4854</v>
       </c>
       <c r="P22" t="n">
-        <v>1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.0907</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3992</v>
+        <v>0.0717</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3166</v>
+        <v>-0.1623</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>0.9317</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.7237</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4515</v>
+        <v>-1.3552</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2985</v>
+        <v>-1.6123</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.153</v>
+        <v>0.2571</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8244</v>
+        <v>-2.8174</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.3233</v>
+        <v>-2.3153</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5011</v>
+        <v>-0.502</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.6906</v>
+        <v>-1.7141</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.424</v>
+        <v>-1.4381</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1338</v>
+        <v>-1.1032</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8993</v>
+        <v>-0.8772</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P23" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2149</v>
+        <v>-0.1312</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6079</v>
+        <v>0.1019</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.607</v>
+        <v>-0.2331</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.402400000000002</v>
+        <v>8.784999999999998</v>
       </c>
       <c r="E24" t="n">
-        <v>17.1817</v>
+        <v>16.8799</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.779</v>
+        <v>-8.095000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.8494</v>
+        <v>-1.788</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0958</v>
+        <v>1.1462</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.9453</v>
+        <v>-2.934</v>
       </c>
       <c r="J24" t="n">
-        <v>9.9458</v>
+        <v>9.725</v>
       </c>
       <c r="K24" t="n">
-        <v>4.6555</v>
+        <v>4.5303</v>
       </c>
       <c r="L24" t="n">
-        <v>5.2901</v>
+        <v>5.1945</v>
       </c>
       <c r="M24" t="n">
-        <v>-11.7953</v>
+        <v>-11.5129</v>
       </c>
       <c r="N24" t="n">
-        <v>-3.5597</v>
+        <v>-3.3845</v>
       </c>
       <c r="O24" t="n">
-        <v>-8.2354</v>
+        <v>-8.128500000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>9.999999999998899e-05</v>
+        <v>9.99999999995449e-05</v>
       </c>
       <c r="Q24" t="n">
-        <v>-11.3417</v>
+        <v>-11.3816</v>
       </c>
       <c r="R24" t="n">
-        <v>11.3417</v>
+        <v>11.3817</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.4497</v>
+        <v>-0.09270000000000014</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9982000000000001</v>
+        <v>1.0189</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.4481</v>
+        <v>-1.1113</v>
       </c>
       <c r="V24" t="n">
-        <v>10.7019</v>
+        <v>10.6655</v>
       </c>
       <c r="W24" t="n">
-        <v>17.5792</v>
+        <v>17.5178</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.8775</v>
+        <v>-6.852499999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104567_W13.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104567_W13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-2.1075</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-17.5177</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104567_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-6.852499999999999</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
